--- a/synchronous_fifo/testsuite/simple_linear_fifo_testplan.xlsx
+++ b/synchronous_fifo/testsuite/simple_linear_fifo_testplan.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dhruv\druvesque\git_src\fifo\synchronous_fifo\testsuite\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A7773252-CDBA-4271-881B-E6FCFB040660}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96B9F4E4-6A4A-4C3E-8D48-F14A4B032C36}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{5DC70CAD-5A36-44E2-902C-2205856ACE47}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="18">
   <si>
     <t>S.No</t>
   </si>
@@ -42,9 +42,6 @@
     <t>Observed Behaviour</t>
   </si>
   <si>
-    <t>Linear Simple FIFO</t>
-  </si>
-  <si>
     <t>Whether the FIFO is empty or not at write_ptr == read_ptr</t>
   </si>
   <si>
@@ -70,6 +67,18 @@
   </si>
   <si>
     <t>Interleaving?</t>
+  </si>
+  <si>
+    <t>Synchronous: Linear Simple FIFO</t>
+  </si>
+  <si>
+    <t>Synchronous: Circular FIFO</t>
+  </si>
+  <si>
+    <t>Asynchronous: Linear Simple FIFO</t>
+  </si>
+  <si>
+    <t>Asynchronous: Circular FIFO</t>
   </si>
 </sst>
 </file>
@@ -454,7 +463,7 @@
   <dimension ref="A1:E22"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="16" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="27.6640625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="4.88671875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="49" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="17.33203125" bestFit="1" customWidth="1"/>
@@ -487,13 +496,13 @@
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="B3" s="2">
         <v>1</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D3" s="2"/>
       <c r="E3" s="2"/>
@@ -504,7 +513,7 @@
         <v>2</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D4" s="2"/>
       <c r="E4" s="2"/>
@@ -515,7 +524,7 @@
         <v>3</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D5" s="2"/>
       <c r="E5" s="2"/>
@@ -526,7 +535,7 @@
         <v>4</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D6" s="2"/>
       <c r="E6" s="2"/>
@@ -537,7 +546,7 @@
         <v>5</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D7" s="2"/>
       <c r="E7" s="2"/>
@@ -548,7 +557,7 @@
         <v>6</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D8" s="2"/>
       <c r="E8" s="2"/>
@@ -559,7 +568,7 @@
         <v>7</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D9" s="2"/>
       <c r="E9" s="2"/>
@@ -570,7 +579,7 @@
         <v>8</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D10" s="2"/>
       <c r="E10" s="2"/>
@@ -581,7 +590,7 @@
         <v>9</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D11" s="2"/>
       <c r="E11" s="2"/>
@@ -601,7 +610,9 @@
       <c r="E13" s="2"/>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A14" s="2"/>
+      <c r="A14" s="2" t="s">
+        <v>15</v>
+      </c>
       <c r="B14" s="2"/>
       <c r="C14" s="2"/>
       <c r="D14" s="2"/>
@@ -622,7 +633,9 @@
       <c r="E16" s="2"/>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A17" s="2"/>
+      <c r="A17" s="2" t="s">
+        <v>16</v>
+      </c>
       <c r="B17" s="2"/>
       <c r="C17" s="2"/>
       <c r="D17" s="2"/>
@@ -643,7 +656,9 @@
       <c r="E19" s="2"/>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A20" s="2"/>
+      <c r="A20" s="2" t="s">
+        <v>17</v>
+      </c>
       <c r="B20" s="2"/>
       <c r="C20" s="2"/>
       <c r="D20" s="2"/>
